--- a/GATEWAY/A1#111DEDALUS0000/DEDALUS/O4C/6.6.0/accreditamento-checklist_V6.6.0.xlsx
+++ b/GATEWAY/A1#111DEDALUS0000/DEDALUS/O4C/6.6.0/accreditamento-checklist_V6.6.0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dedalusspa-my.sharepoint.com/personal/marco_difalco_dedalus_eu/Documents/Desktop/accreditamento/accreditamento-fse/esempi/O4C/6.6.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="13_ncr:1_{75FC5719-B4C9-497D-AB4F-9083CDB6E2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F96CC7C8-D2B4-4197-ACFC-886A1399C391}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="13_ncr:1_{75FC5719-B4C9-497D-AB4F-9083CDB6E2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{147BAC6C-46E3-4467-8E80-A4EDB6B42E1C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TestCases!$A$9:$W$191</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -80,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="494">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -1867,6 +1868,21 @@
   </si>
   <si>
     <t>2.16.840.1.113883.2.9.2.10212.4.4.1.d22db0e570a9c27132303b8c0fc13ac5acb7547931495c4d26c557ec2112d3fd.e5d260e33b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>54295c963b119bfba6861e34c0c3a520</t>
+  </si>
+  <si>
+    <t>UNKNOWN_WORKFLOW_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06-17:T13:47:34 </t>
+  </si>
+  <si>
+    <t>2025-06-17T13:49:22</t>
+  </si>
+  <si>
+    <t>e4cf27abbbdbc2cd3ac438940891a443</t>
   </si>
 </sst>
 </file>
@@ -3949,7 +3965,7 @@
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
     <col min="2" max="2" width="46.77734375" customWidth="1"/>
     <col min="3" max="3" width="20.21875" customWidth="1"/>
-    <col min="4" max="4" width="63.77734375" customWidth="1"/>
+    <col min="4" max="4" width="45.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="47.5546875" customWidth="1"/>
     <col min="6" max="6" width="33.21875" style="45" customWidth="1"/>
     <col min="7" max="8" width="33.21875" customWidth="1"/>
@@ -4416,7 +4432,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="10.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="31">
         <v>32</v>
       </c>
@@ -4432,25 +4448,45 @@
       <c r="E15" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="39"/>
+      <c r="F15" s="33">
+        <v>45825</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>491</v>
+      </c>
+      <c r="H15" s="33" t="s">
+        <v>489</v>
+      </c>
+      <c r="I15" s="39" t="s">
+        <v>490</v>
+      </c>
       <c r="J15" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="K15" s="29" t="s">
-        <v>239</v>
-      </c>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
+      <c r="N15" s="29" t="s">
+        <v>234</v>
+      </c>
       <c r="O15" s="29"/>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="29"/>
-      <c r="S15" s="29"/>
-      <c r="T15" s="29"/>
+      <c r="P15" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q15" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="R15" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="S15" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="T15" s="29" t="s">
+        <v>232</v>
+      </c>
       <c r="U15" s="34"/>
       <c r="V15" s="35"/>
       <c r="W15" s="29" t="s">
@@ -4732,25 +4768,45 @@
       <c r="E23" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="39"/>
+      <c r="F23" s="33">
+        <v>45825</v>
+      </c>
+      <c r="G23" s="33" t="s">
+        <v>492</v>
+      </c>
+      <c r="H23" s="33" t="s">
+        <v>493</v>
+      </c>
+      <c r="I23" s="39" t="s">
+        <v>490</v>
+      </c>
       <c r="J23" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="K23" s="29" t="s">
-        <v>239</v>
-      </c>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
+      <c r="N23" s="29" t="s">
+        <v>234</v>
+      </c>
       <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
+      <c r="P23" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q23" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="R23" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="S23" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="T23" s="29" t="s">
+        <v>232</v>
+      </c>
       <c r="U23" s="34"/>
       <c r="V23" s="35"/>
       <c r="W23" s="29" t="s">
@@ -15482,19 +15538,19 @@
           <x14:formula1>
             <xm:f>Sheet1!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>M14:N14 P14:R14 J14:J20 M16:N20 P16:R20 M22:N22 P22:R22 J22:J28 M24:N28 P24:R28 P10:R12 M10:N12 J10:J12 M30:N180 Q170:R171 P182:Q182 P189:R189 P171 P30:R169 P172:R180 J30:J180</xm:sqref>
+          <xm:sqref>M14:N14 J14:J20 M16:N20 M22:N22 J22:J28 M24:N28 P10:R12 M10:N12 J10:J12 M30:N180 Q170:R171 P182:Q182 P189:R189 P171 P30:R169 P172:R180 J30:J180 P14:R20 P22:R28</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{70793024-27E9-4E6A-BACD-083AB683BC38}">
           <x14:formula1>
             <xm:f>Sheet1!$A$2:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>T14 T16:T20 T22 T24:T28 T10:T12 T30:T180 T189</xm:sqref>
+          <xm:sqref>T14:T20 T22:T28 T10:T12 T30:T180 T189</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3DE61C5E-9DA3-4CE3-A1FF-8FBE651EA6B5}">
           <x14:formula1>
             <xm:f>'LISTA VALORI'!$A$2:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>K10:K180 K182</xm:sqref>
+          <xm:sqref>K182 K10:K180</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -17731,27 +17787,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d4db60622090a1f8a8d506ac1d64a349">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a3a9ed8bb952a3d76dd1e2fa3d624b9" ns2:_="" ns3:_="">
     <xsd:import namespace="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
@@ -18009,32 +18044,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CE213DB-5082-48B0-B2A5-099EBF944035}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18051,4 +18082,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/GATEWAY/A1#111DEDALUS0000/DEDALUS/O4C/6.6.0/accreditamento-checklist_V6.6.0.xlsx
+++ b/GATEWAY/A1#111DEDALUS0000/DEDALUS/O4C/6.6.0/accreditamento-checklist_V6.6.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dedalusspa-my.sharepoint.com/personal/marco_difalco_dedalus_eu/Documents/Desktop/accreditamento/accreditamento-fse/esempi/O4C/6.6.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="13_ncr:1_{75FC5719-B4C9-497D-AB4F-9083CDB6E2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{147BAC6C-46E3-4467-8E80-A4EDB6B42E1C}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="13_ncr:1_{75FC5719-B4C9-497D-AB4F-9083CDB6E2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAFBF15D-DBEC-4DD6-9AA2-61EA1AA52029}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TestCases!$A$9:$W$191</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -81,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="494">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -4461,9 +4460,11 @@
         <v>490</v>
       </c>
       <c r="J15" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="K15" s="29"/>
+        <v>234</v>
+      </c>
+      <c r="K15" s="29" t="s">
+        <v>244</v>
+      </c>
       <c r="L15" s="29"/>
       <c r="M15" s="29" t="s">
         <v>234</v>
@@ -4781,9 +4782,11 @@
         <v>490</v>
       </c>
       <c r="J23" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="K23" s="29"/>
+        <v>234</v>
+      </c>
+      <c r="K23" s="29" t="s">
+        <v>244</v>
+      </c>
       <c r="L23" s="29"/>
       <c r="M23" s="29" t="s">
         <v>234</v>
